--- a/diseases/d043/1995-1999.xlsx
+++ b/diseases/d043/1995-1999.xlsx
@@ -773,6 +773,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1223,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1373,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1498,6 +1523,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1643,6 +1673,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1788,6 +1823,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1933,6 +1973,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2078,6 +2123,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2223,6 +2273,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2368,6 +2423,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2513,6 +2573,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2658,6 +2723,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2803,6 +2873,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2948,6 +3023,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3173,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3238,6 +3323,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3473,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3623,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3773,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3818,6 +3923,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3963,6 +4073,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4108,6 +4223,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4253,6 +4373,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4398,6 +4523,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4543,6 +4673,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4688,6 +4823,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4833,6 +4973,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4978,6 +5123,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5123,6 +5273,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5268,6 +5423,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5413,6 +5573,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5558,6 +5723,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5703,6 +5873,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5846,6 +6021,11 @@
       <c r="S37" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">

--- a/diseases/d043/1995-1999.xlsx
+++ b/diseases/d043/1995-1999.xlsx
@@ -768,11 +768,6 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,11 +903,6 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,22 +915,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1068,11 +1038,6 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,22 +1050,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1218,11 +1173,6 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1235,22 +1185,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1368,11 +1308,6 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1385,22 +1320,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1518,11 +1443,6 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1535,22 +1455,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1668,11 +1578,6 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1685,22 +1590,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1818,11 +1713,6 @@
       <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1835,22 +1725,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1968,11 +1848,6 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1985,22 +1860,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2118,11 +1983,6 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2135,22 +1995,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2268,11 +2118,6 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2285,22 +2130,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2418,11 +2253,6 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2435,22 +2265,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2568,11 +2388,6 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2585,22 +2400,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2718,11 +2523,6 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2735,22 +2535,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2868,11 +2658,6 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2885,22 +2670,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3018,11 +2793,6 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3035,22 +2805,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3168,11 +2928,6 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3185,22 +2940,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3318,11 +3063,6 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,22 +3075,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3468,11 +3198,6 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3485,22 +3210,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3618,11 +3333,6 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3635,22 +3345,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3768,11 +3468,6 @@
       <c r="Q22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3785,22 +3480,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3918,11 +3603,6 @@
       <c r="Q23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3935,22 +3615,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4068,11 +3738,6 @@
       <c r="Q24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4085,22 +3750,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4218,11 +3873,6 @@
       <c r="Q25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4235,22 +3885,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4368,11 +4008,6 @@
       <c r="Q26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4385,22 +4020,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4518,11 +4143,6 @@
       <c r="Q27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4535,22 +4155,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4668,11 +4278,6 @@
       <c r="Q28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4685,22 +4290,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4818,11 +4413,6 @@
       <c r="Q29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4835,22 +4425,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4968,11 +4548,6 @@
       <c r="Q30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4985,22 +4560,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5118,11 +4683,6 @@
       <c r="Q31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5135,22 +4695,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5268,11 +4818,6 @@
       <c r="Q32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5285,22 +4830,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5418,11 +4953,6 @@
       <c r="Q33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5435,22 +4965,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5568,11 +5088,6 @@
       <c r="Q34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5585,22 +5100,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5718,11 +5223,6 @@
       <c r="Q35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5735,22 +5235,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5868,11 +5358,6 @@
       <c r="Q36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5885,22 +5370,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6018,11 +5493,6 @@
       <c r="Q37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6035,22 +5505,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>

--- a/diseases/d043/1995-1999.xlsx
+++ b/diseases/d043/1995-1999.xlsx
@@ -768,6 +768,11 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,12 +785,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -903,6 +918,11 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,12 +935,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1038,6 +1068,11 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,12 +1085,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1173,6 +1218,11 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1185,12 +1235,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1308,6 +1368,11 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1320,12 +1385,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1443,6 +1518,11 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1455,12 +1535,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1578,6 +1668,11 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1590,12 +1685,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1713,6 +1818,11 @@
       <c r="Q9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1725,12 +1835,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1848,6 +1968,11 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1860,12 +1985,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -1983,6 +2118,11 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1995,12 +2135,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2118,6 +2268,11 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2130,12 +2285,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2253,6 +2418,11 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2265,12 +2435,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2388,6 +2568,11 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2400,12 +2585,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2523,6 +2718,11 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2535,12 +2735,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2658,6 +2868,11 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2670,12 +2885,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2793,6 +3018,11 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2805,12 +3035,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2928,6 +3168,11 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2940,12 +3185,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3063,6 +3318,11 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3075,12 +3335,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3198,6 +3468,11 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3210,12 +3485,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3333,6 +3618,11 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3345,12 +3635,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3468,6 +3768,11 @@
       <c r="Q22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3480,12 +3785,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3603,6 +3918,11 @@
       <c r="Q23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3615,12 +3935,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3738,6 +4068,11 @@
       <c r="Q24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3750,12 +4085,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -3873,6 +4218,11 @@
       <c r="Q25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3885,12 +4235,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4008,6 +4368,11 @@
       <c r="Q26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4020,12 +4385,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4143,6 +4518,11 @@
       <c r="Q27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4155,12 +4535,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4278,6 +4668,11 @@
       <c r="Q28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4290,12 +4685,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4413,6 +4818,11 @@
       <c r="Q29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4425,12 +4835,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4548,6 +4968,11 @@
       <c r="Q30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4560,12 +4985,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4683,6 +5118,11 @@
       <c r="Q31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4695,12 +5135,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4818,6 +5268,11 @@
       <c r="Q32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4830,12 +5285,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -4953,6 +5418,11 @@
       <c r="Q33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4965,12 +5435,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5088,6 +5568,11 @@
       <c r="Q34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5100,12 +5585,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5223,6 +5718,11 @@
       <c r="Q35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5235,12 +5735,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5358,6 +5868,11 @@
       <c r="Q36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5370,12 +5885,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5493,6 +6018,11 @@
       <c r="Q37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5505,12 +6035,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
